--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -463,31 +463,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Message: no such element: Unable to locate element: {"method":"xpath","selector":"//input[@type='text']"}
-  (Session info: chrome=146.0.7680.177); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-#0 0x61f8918e0252 &lt;unknown&gt;
-#1 0x61f8912b0226 &lt;unknown&gt;
-#2 0x61f891301c2c &lt;unknown&gt;
-#3 0x61f891301e45 &lt;unknown&gt;
-#4 0x61f89134bf98 &lt;unknown&gt;
-#5 0x61f891327231 &lt;unknown&gt;
-#6 0x61f8913497d1 &lt;unknown&gt;
-#7 0x61f891326fa7 &lt;unknown&gt;
-#8 0x61f8912f4de2 &lt;unknown&gt;
-#9 0x61f8912f5c55 &lt;unknown&gt;
-#10 0x61f8918a3ee4 &lt;unknown&gt;
-#11 0x61f8918a7236 &lt;unknown&gt;
-#12 0x61f8918a6cee &lt;unknown&gt;
-#13 0x61f8918a76a9 &lt;unknown&gt;
-#14 0x61f8918936ea &lt;unknown&gt;
-#15 0x61f8918a7a2a &lt;unknown&gt;
-#16 0x61f89187c359 &lt;unknown&gt;
-#17 0x61f8918ccf79 &lt;unknown&gt;
-#18 0x61f8918cd16d &lt;unknown&gt;
-#19 0x61f8918dec8e &lt;unknown&gt;
-#20 0x74bbd25b2b7b &lt;unknown&gt;
-</t>
+          <t>No se encontró el input del DNI después de 15 segundos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -509,31 +485,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Message: no such element: Unable to locate element: {"method":"xpath","selector":"//input[@type='text']"}
-  (Session info: chrome=146.0.7680.177); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-#0 0x61f8918e0252 &lt;unknown&gt;
-#1 0x61f8912b0226 &lt;unknown&gt;
-#2 0x61f891301c2c &lt;unknown&gt;
-#3 0x61f891301e45 &lt;unknown&gt;
-#4 0x61f89134bf98 &lt;unknown&gt;
-#5 0x61f891327231 &lt;unknown&gt;
-#6 0x61f8913497d1 &lt;unknown&gt;
-#7 0x61f891326fa7 &lt;unknown&gt;
-#8 0x61f8912f4de2 &lt;unknown&gt;
-#9 0x61f8912f5c55 &lt;unknown&gt;
-#10 0x61f8918a3ee4 &lt;unknown&gt;
-#11 0x61f8918a7236 &lt;unknown&gt;
-#12 0x61f8918a6cee &lt;unknown&gt;
-#13 0x61f8918a76a9 &lt;unknown&gt;
-#14 0x61f8918936ea &lt;unknown&gt;
-#15 0x61f8918a7a2a &lt;unknown&gt;
-#16 0x61f89187c359 &lt;unknown&gt;
-#17 0x61f8918ccf79 &lt;unknown&gt;
-#18 0x61f8918cd16d &lt;unknown&gt;
-#19 0x61f8918dec8e &lt;unknown&gt;
-#20 0x74bbd25b2b7b &lt;unknown&gt;
-</t>
+          <t>No se encontró el input del DNI después de 15 segundos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -555,31 +507,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Message: no such element: Unable to locate element: {"method":"xpath","selector":"//input[@type='text']"}
-  (Session info: chrome=146.0.7680.177); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-#0 0x61f8918e0252 &lt;unknown&gt;
-#1 0x61f8912b0226 &lt;unknown&gt;
-#2 0x61f891301c2c &lt;unknown&gt;
-#3 0x61f891301e45 &lt;unknown&gt;
-#4 0x61f89134bf98 &lt;unknown&gt;
-#5 0x61f891327231 &lt;unknown&gt;
-#6 0x61f8913497d1 &lt;unknown&gt;
-#7 0x61f891326fa7 &lt;unknown&gt;
-#8 0x61f8912f4de2 &lt;unknown&gt;
-#9 0x61f8912f5c55 &lt;unknown&gt;
-#10 0x61f8918a3ee4 &lt;unknown&gt;
-#11 0x61f8918a7236 &lt;unknown&gt;
-#12 0x61f8918a6cee &lt;unknown&gt;
-#13 0x61f8918a76a9 &lt;unknown&gt;
-#14 0x61f8918936ea &lt;unknown&gt;
-#15 0x61f8918a7a2a &lt;unknown&gt;
-#16 0x61f89187c359 &lt;unknown&gt;
-#17 0x61f8918ccf79 &lt;unknown&gt;
-#18 0x61f8918cd16d &lt;unknown&gt;
-#19 0x61f8918dec8e &lt;unknown&gt;
-#20 0x74bbd25b2b7b &lt;unknown&gt;
-</t>
+          <t>No se encontró el input del DNI después de 15 segundos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>No se encontró el input del DNI después de 15 segundos</t>
+          <t>No se encontró ningún input en la página</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No se encontró el input del DNI después de 15 segundos</t>
+          <t>No se encontró ningún input en la página</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No se encontró el input del DNI después de 15 segundos</t>
+          <t>No se encontró ningún input en la página</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>No se encontró ningún input en la página</t>
+          <t>No encontrada</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No encontrada</t>
         </is>
       </c>
     </row>
@@ -480,17 +480,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No se encontró ningún input en la página</t>
+          <t>No encontrada</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No encontrada</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No se encontró ningún input en la página</t>
+          <t>No encontrada</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No encontrada</t>
         </is>
       </c>
     </row>
